--- a/data/batches/B09_AllDomain_columns_and_derived_DY/Test_Validation_Report/Test_Validation_Report_B09.xlsx
+++ b/data/batches/B09_AllDomain_columns_and_derived_DY/Test_Validation_Report/Test_Validation_Report_B09.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -724,7 +724,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -822,7 +822,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>FAIL - Domain mismatch</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -11312,11 +11312,7 @@
           <t>DM</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>CUSTOMVAR</t>
@@ -11324,25 +11320,49 @@
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Column not present in original</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Column not present in original</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>New column injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -11367,11 +11387,7 @@
           <t>DM</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>AGETXT</t>
@@ -11379,25 +11395,49 @@
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Column not present in original</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Column not present in original</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>THIRTY-FIVE</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>THIRTY-FIVE</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>New column injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -11422,11 +11462,7 @@
           <t>DM</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>SETCD</t>
@@ -11434,25 +11470,49 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Column not present in original</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Column not present in original</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>ITT</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>ITT</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>New column injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -11477,11 +11537,7 @@
           <t>DM</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>STUDYID&lt;-&gt;DOMAIN</t>
@@ -11532,11 +11588,7 @@
           <t>CO</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>CODY</t>
@@ -11544,25 +11596,49 @@
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -11587,11 +11663,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>EGTPT</t>
@@ -11599,25 +11671,49 @@
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -11642,11 +11738,7 @@
           <t>PC</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>PCTPT</t>
@@ -11654,25 +11746,49 @@
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -11697,11 +11813,7 @@
           <t>VS</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>VSTPT</t>
@@ -11709,25 +11821,49 @@
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -11752,11 +11888,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>EGTPTREF</t>
@@ -11764,25 +11896,49 @@
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -11807,11 +11963,7 @@
           <t>PC</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>PCTPTREF</t>
@@ -11819,25 +11971,49 @@
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -11862,11 +12038,7 @@
           <t>VS</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>VSTPTREF</t>
@@ -11874,25 +12046,49 @@
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -11917,11 +12113,7 @@
           <t>EG</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>EGRFTDTC</t>
@@ -11929,25 +12121,49 @@
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -11972,11 +12188,7 @@
           <t>PC</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>PCRFTDTC</t>
@@ -11984,25 +12196,49 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -12027,11 +12263,7 @@
           <t>VS</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>VSRFTDTC</t>
@@ -12039,25 +12271,49 @@
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -12331,7 +12587,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -12382,7 +12638,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -12527,7 +12783,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -12578,7 +12834,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -12723,7 +12979,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -12774,7 +13030,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>FAIL - Domain mismatch</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -13002,10 +13258,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -13020,7 +13276,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>38.46</v>
+        <v>84.62</v>
       </c>
     </row>
   </sheetData>
